--- a/table/tableList_protocolCore.xlsx
+++ b/table/tableList_protocolCore.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcorbara\Documents\ArgoX3_API_Mobile_CORE\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB6D5AE0-B12E-474D-8238-E7B060432349}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABDEE4DB-6282-408C-A13A-815599C085EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nuove tabelle" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="112">
   <si>
     <t>Tabella</t>
   </si>
@@ -360,6 +360,9 @@
   </si>
   <si>
     <t>EXPIRY</t>
+  </si>
+  <si>
+    <t>YAX3MDEMOINF</t>
   </si>
 </sst>
 </file>
@@ -571,7 +574,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -726,7 +729,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1007,23 +1009,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.88671875" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" customWidth="1"/>
-    <col min="3" max="3" width="32.44140625" customWidth="1"/>
-    <col min="4" max="4" width="11.44140625" customWidth="1"/>
-    <col min="5" max="5" width="15.88671875" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" customWidth="1"/>
-    <col min="7" max="7" width="14.88671875" customWidth="1"/>
-    <col min="8" max="8" width="17.88671875" customWidth="1"/>
-    <col min="9" max="9" width="20.109375" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" customWidth="1"/>
-    <col min="11" max="11" width="16.6640625" customWidth="1"/>
+    <col min="1" max="1" width="20.85546875" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+    <col min="3" max="3" width="32.42578125" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" customWidth="1"/>
+    <col min="8" max="8" width="17.85546875" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" customWidth="1"/>
+    <col min="11" max="11" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="46" t="s">
         <v>2</v>
       </c>
@@ -1058,11 +1060,11 @@
         <v>108</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="47"/>
       <c r="B2" s="47"/>
     </row>
-    <row r="3" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="50" t="s">
         <v>12</v>
       </c>
@@ -1095,7 +1097,7 @@
       </c>
       <c r="K3" s="4"/>
     </row>
-    <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -1114,7 +1116,7 @@
       </c>
       <c r="K4" s="4"/>
     </row>
-    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -1126,7 +1128,7 @@
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
     </row>
-    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="50" t="s">
         <v>18</v>
       </c>
@@ -1158,8 +1160,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="50" t="s">
         <v>102</v>
       </c>
@@ -1190,9 +1192,8 @@
       <c r="J8" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="K8" s="54"/>
-    </row>
-    <row r="9" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H9" s="34" t="s">
         <v>106</v>
       </c>
@@ -1202,7 +1203,11 @@
       <c r="J9" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="K9" s="54"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>111</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1213,20 +1218,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C6CAB61-4E19-4D48-B29B-AF9E6005A9F4}">
   <dimension ref="A1:N28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.109375" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.88671875" customWidth="1"/>
-    <col min="6" max="6" width="16.33203125" customWidth="1"/>
+    <col min="1" max="1" width="20.140625" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="17.109375" customWidth="1"/>
-    <col min="12" max="12" width="20.6640625" customWidth="1"/>
-    <col min="13" max="13" width="13.88671875" customWidth="1"/>
-    <col min="14" max="14" width="24.5546875" customWidth="1"/>
+    <col min="11" max="11" width="17.140625" customWidth="1"/>
+    <col min="12" max="12" width="20.7109375" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" customWidth="1"/>
+    <col min="14" max="14" width="24.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1270,8 +1275,8 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="1:14" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:14" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="42" t="s">
         <v>35</v>
       </c>
@@ -1311,11 +1316,11 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F4" s="45"/>
       <c r="N4" s="6"/>
     </row>
-    <row r="5" spans="1:14" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="43" t="s">
         <v>42</v>
       </c>
@@ -1355,11 +1360,11 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F6" s="45"/>
       <c r="N6" s="6"/>
     </row>
-    <row r="7" spans="1:14" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="43" t="s">
         <v>45</v>
       </c>
@@ -1399,11 +1404,11 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F8" s="40"/>
       <c r="N8" s="6"/>
     </row>
-    <row r="9" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="49" t="s">
         <v>12</v>
       </c>
@@ -1443,7 +1448,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="44"/>
       <c r="B10" s="5" t="s">
         <v>54</v>
@@ -1485,7 +1490,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="44"/>
       <c r="B11" s="5" t="s">
         <v>93</v>
@@ -1521,7 +1526,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="44"/>
       <c r="B12" s="5" t="s">
         <v>58</v>
@@ -1559,7 +1564,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="44"/>
       <c r="B13" s="5" t="s">
         <v>61</v>
@@ -1597,7 +1602,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="44"/>
       <c r="B14" s="6" t="s">
         <v>72</v>
@@ -1635,7 +1640,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="37"/>
       <c r="B15" s="18" t="s">
         <v>67</v>
@@ -1673,12 +1678,12 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
       <c r="F16" s="40"/>
       <c r="N16" s="6"/>
     </row>
-    <row r="17" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="49" t="s">
         <v>18</v>
       </c>
@@ -1696,7 +1701,7 @@
       <c r="M17" s="15"/>
       <c r="N17" s="16"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="44"/>
       <c r="B18" s="5" t="s">
         <v>54</v>
@@ -1738,7 +1743,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="44"/>
       <c r="B19" s="27" t="s">
         <v>73</v>
@@ -1776,7 +1781,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="44"/>
       <c r="B20" s="5" t="s">
         <v>76</v>
@@ -1814,7 +1819,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="44"/>
       <c r="B21" s="5" t="s">
         <v>80</v>
@@ -1852,7 +1857,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="44"/>
       <c r="B22" s="5" t="s">
         <v>82</v>
@@ -1890,7 +1895,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="44"/>
       <c r="B23" s="5" t="s">
         <v>85</v>
@@ -1928,7 +1933,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="37"/>
       <c r="B24" s="18" t="s">
         <v>88</v>
@@ -1966,8 +1971,8 @@
         <v>89</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="26" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="48" t="s">
         <v>102</v>
       </c>
@@ -2011,7 +2016,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="41"/>
       <c r="B27" s="53" t="s">
         <v>107</v>
@@ -2043,7 +2048,7 @@
       <c r="M27" s="4"/>
       <c r="N27" s="52"/>
     </row>
-    <row r="28" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="34"/>
       <c r="B28" s="34" t="s">
         <v>110</v>
@@ -2084,15 +2089,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCE8AA00-09A4-49FF-BAFD-B0681AA08F5E}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="16.44140625" customWidth="1"/>
-    <col min="3" max="3" width="29.109375" customWidth="1"/>
-    <col min="4" max="4" width="11.109375" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" customWidth="1"/>
+    <col min="3" max="3" width="29.140625" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -2109,14 +2114,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="30"/>
       <c r="B2" s="30"/>
       <c r="C2" s="30"/>
       <c r="D2" s="30"/>
       <c r="E2" s="30"/>
     </row>
-    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="49" t="s">
         <v>12</v>
       </c>
@@ -2133,7 +2138,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="37"/>
       <c r="B4" s="35" t="s">
         <v>98</v>
@@ -2148,14 +2153,14 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="51" t="s">
         <v>18</v>
       </c>
@@ -2172,8 +2177,8 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="49" t="s">
         <v>102</v>
       </c>
@@ -2190,7 +2195,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="37"/>
       <c r="B9" s="35" t="s">
         <v>106</v>

--- a/table/tableList_protocolCore.xlsx
+++ b/table/tableList_protocolCore.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcorbara\Documents\ArgoX3_API_Mobile_CORE\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABDEE4DB-6282-408C-A13A-815599C085EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B579F4C-1964-4669-BA2A-86E3826C1D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23280" yWindow="2715" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Nuove tabelle" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="114">
   <si>
     <t>Tabella</t>
   </si>
@@ -353,9 +353,6 @@
     <t>TOKENHASH</t>
   </si>
   <si>
-    <t>Patch</t>
-  </si>
-  <si>
     <t>Noù</t>
   </si>
   <si>
@@ -363,6 +360,15 @@
   </si>
   <si>
     <t>YAX3MDEMOINF</t>
+  </si>
+  <si>
+    <t>Codice Tipo per Patch</t>
+  </si>
+  <si>
+    <t>ATB</t>
+  </si>
+  <si>
+    <t>Note per Patch</t>
   </si>
 </sst>
 </file>
@@ -406,7 +412,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -570,11 +576,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -582,9 +612,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -709,9 +736,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -729,6 +753,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1009,204 +1042,229 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.85546875" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
-    <col min="3" max="3" width="32.42578125" customWidth="1"/>
+    <col min="3" max="3" width="27.42578125" customWidth="1"/>
     <col min="4" max="4" width="11.42578125" customWidth="1"/>
     <col min="5" max="5" width="15.85546875" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" customWidth="1"/>
     <col min="7" max="7" width="14.85546875" customWidth="1"/>
     <col min="8" max="8" width="17.85546875" customWidth="1"/>
     <col min="9" max="9" width="20.140625" customWidth="1"/>
     <col min="10" max="10" width="10.7109375" customWidth="1"/>
-    <col min="11" max="11" width="16.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
+    <row r="1" spans="1:12" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="46" t="s">
+      <c r="B1" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
-    </row>
-    <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="50" t="s">
+      <c r="K1" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="45"/>
+      <c r="B2" s="45"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+    </row>
+    <row r="3" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="38" t="s">
+      <c r="C3" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="E3" s="38" t="s">
+      <c r="D3" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="E3" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="38" t="s">
+      <c r="F3" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="38" t="s">
+      <c r="G3" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="31" t="s">
+      <c r="H3" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="32" t="s">
+      <c r="I3" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="J3" s="33" t="s">
+      <c r="J3" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="4"/>
-    </row>
-    <row r="4" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="34" t="s">
+      <c r="K3" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="L3" s="53"/>
+    </row>
+    <row r="4" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="I4" s="35" t="s">
+      <c r="I4" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="J4" s="36" t="s">
+      <c r="J4" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="K4" s="4"/>
-    </row>
-    <row r="5" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-    </row>
-    <row r="6" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="50" t="s">
+      <c r="K4" s="53"/>
+      <c r="L4" s="53"/>
+    </row>
+    <row r="5" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="K5" s="53"/>
+      <c r="L5" s="54"/>
+    </row>
+    <row r="6" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="C6" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="E6" s="38" t="s">
+      <c r="D6" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="38" t="s">
+      <c r="F6" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="G6" s="38" t="s">
+      <c r="G6" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="48" t="s">
+      <c r="H6" s="46" t="s">
         <v>92</v>
       </c>
-      <c r="I6" s="38" t="s">
+      <c r="I6" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="J6" s="22" t="s">
+      <c r="J6" s="37" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="50" t="s">
+      <c r="K6" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="L6" s="54"/>
+    </row>
+    <row r="7" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K7" s="54"/>
+      <c r="L7" s="54"/>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="48" t="s">
         <v>102</v>
       </c>
-      <c r="B8" s="38" t="s">
+      <c r="B8" s="37" t="s">
         <v>103</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="37" t="s">
         <v>104</v>
       </c>
-      <c r="D8" s="38" t="s">
-        <v>95</v>
-      </c>
-      <c r="E8" s="38" t="s">
+      <c r="D8" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="E8" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="38" t="s">
+      <c r="F8" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="38" t="s">
+      <c r="G8" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="31" t="s">
+      <c r="H8" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="I8" s="32" t="s">
+      <c r="I8" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="J8" s="33" t="s">
+      <c r="J8" s="31" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H9" s="34" t="s">
+      <c r="K8" s="53" t="s">
+        <v>112</v>
+      </c>
+      <c r="L8" s="54"/>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H9" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="I9" s="35" t="s">
+      <c r="I9" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="J9" s="36" t="s">
+      <c r="J9" s="34" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>111</v>
+      <c r="K9" s="53"/>
+      <c r="L9" s="54"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="56" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -1235,850 +1293,850 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="6" t="s">
         <v>31</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="N1" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:14" ht="42.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="41" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="9">
         <v>1</v>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="9">
         <v>4</v>
       </c>
-      <c r="F3" s="39" t="s">
+      <c r="F3" s="38" t="s">
         <v>101</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="9">
         <v>15</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
-      <c r="L3" s="10" t="s">
+      <c r="I3" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="M3" s="10" t="s">
+      <c r="M3" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="N3" s="10" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F4" s="45"/>
-      <c r="N4" s="6"/>
+      <c r="F4" s="44"/>
+      <c r="N4" s="5"/>
     </row>
     <row r="5" spans="1:14" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="42" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="9">
         <v>6911</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="9">
         <v>15</v>
       </c>
-      <c r="F5" s="39" t="s">
+      <c r="F5" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="9">
         <v>15</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10" t="s">
+      <c r="I5" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="M5" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="N5" s="11" t="s">
+      <c r="N5" s="10" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F6" s="45"/>
-      <c r="N6" s="6"/>
+      <c r="F6" s="44"/>
+      <c r="N6" s="5"/>
     </row>
     <row r="7" spans="1:14" ht="40.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="43" t="s">
+      <c r="A7" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <v>1</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="9">
         <v>4</v>
       </c>
-      <c r="F7" s="39" t="s">
+      <c r="F7" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="9">
         <v>15</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10" t="s">
+      <c r="I7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="M7" s="10" t="s">
+      <c r="M7" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="N7" s="11" t="s">
+      <c r="N7" s="10" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F8" s="40"/>
-      <c r="N8" s="6"/>
+      <c r="F8" s="39"/>
+      <c r="N8" s="5"/>
     </row>
     <row r="9" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="49" t="s">
+      <c r="A9" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="13">
+      <c r="D9" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="12">
         <v>30</v>
       </c>
-      <c r="F9" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="G9" s="13">
+      <c r="F9" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="G9" s="12">
         <v>1</v>
       </c>
-      <c r="H9" s="13" t="s">
+      <c r="H9" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="I9" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="15" t="s">
+      <c r="I9" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="M9" s="15" t="s">
+      <c r="M9" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="N9" s="16" t="s">
+      <c r="N9" s="15" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="44"/>
-      <c r="B10" s="5" t="s">
+      <c r="A10" s="43"/>
+      <c r="B10" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" s="6">
+      <c r="D10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="5">
         <v>30</v>
       </c>
-      <c r="F10" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="G10" s="6">
+      <c r="F10" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="G10" s="5">
         <v>1</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="I10" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="J10" s="6" t="s">
+      <c r="I10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J10" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="L10" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="M10" s="6" t="s">
+      <c r="M10" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="N10" s="17" t="s">
+      <c r="N10" s="16" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="44"/>
-      <c r="B11" s="5" t="s">
+      <c r="A11" s="43"/>
+      <c r="B11" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <v>1</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="5">
         <v>4</v>
       </c>
-      <c r="F11" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="G11" s="6">
+      <c r="F11" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="G11" s="5">
         <v>1</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6" t="s">
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+      <c r="K11" s="5"/>
+      <c r="L11" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="M11" s="6" t="s">
+      <c r="M11" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="N11" s="17" t="s">
+      <c r="N11" s="16" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="44"/>
-      <c r="B12" s="5" t="s">
+      <c r="A12" s="43"/>
+      <c r="B12" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E12" s="6">
+      <c r="D12" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E12" s="5">
         <v>50</v>
       </c>
-      <c r="F12" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="G12" s="6">
+      <c r="F12" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="G12" s="5">
         <v>1</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="I12" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6" t="s">
+      <c r="I12" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="M12" s="6" t="s">
+      <c r="M12" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="N12" s="17" t="s">
+      <c r="N12" s="16" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="44"/>
-      <c r="B13" s="5" t="s">
+      <c r="A13" s="43"/>
+      <c r="B13" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E13" s="6">
+      <c r="D13" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="5">
         <v>50</v>
       </c>
-      <c r="F13" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="G13" s="6">
+      <c r="F13" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="G13" s="5">
         <v>1</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="H13" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="I13" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6" t="s">
+      <c r="I13" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="M13" s="6" t="s">
+      <c r="M13" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="N13" s="17" t="s">
+      <c r="N13" s="16" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="44"/>
-      <c r="B14" s="6" t="s">
+      <c r="A14" s="43"/>
+      <c r="B14" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F14" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="G14" s="6">
+      <c r="D14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="G14" s="5">
         <v>1</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="H14" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="I14" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="6" t="s">
+      <c r="I14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="M14" s="6" t="s">
+      <c r="M14" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="N14" s="17" t="s">
+      <c r="N14" s="16" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="37"/>
-      <c r="B15" s="18" t="s">
+      <c r="A15" s="36"/>
+      <c r="B15" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D15" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="F15" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="G15" s="19">
+      <c r="D15" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="G15" s="18">
         <v>1</v>
       </c>
-      <c r="H15" s="19" t="s">
+      <c r="H15" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="I15" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="J15" s="19"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19" t="s">
+      <c r="I15" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="M15" s="19" t="s">
+      <c r="M15" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="N15" s="20" t="s">
+      <c r="N15" s="19" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="4"/>
-      <c r="F16" s="40"/>
-      <c r="N16" s="6"/>
+      <c r="A16" s="3"/>
+      <c r="F16" s="39"/>
+      <c r="N16" s="5"/>
     </row>
     <row r="17" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="49" t="s">
+      <c r="A17" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="13"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="16"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="14"/>
+      <c r="N17" s="15"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="44"/>
-      <c r="B18" s="5" t="s">
+      <c r="A18" s="43"/>
+      <c r="B18" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E18" s="6">
+      <c r="D18" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E18" s="5">
         <v>30</v>
       </c>
-      <c r="F18" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="G18" s="6">
+      <c r="F18" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="G18" s="5">
         <v>1</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="H18" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="I18" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="J18" s="6" t="s">
+      <c r="I18" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="J18" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="K18" s="6" t="s">
+      <c r="K18" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="L18" s="6" t="s">
+      <c r="L18" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="M18" s="6" t="s">
+      <c r="M18" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="N18" s="17" t="s">
+      <c r="N18" s="16" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="44"/>
-      <c r="B19" s="27" t="s">
+      <c r="A19" s="43"/>
+      <c r="B19" s="26" t="s">
         <v>73</v>
       </c>
-      <c r="C19" s="26" t="s">
+      <c r="C19" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="E19" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="F19" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="G19" s="6">
+      <c r="D19" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="F19" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="G19" s="5">
         <v>1</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="H19" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="I19" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="6" t="s">
+      <c r="I19" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="J19" s="27"/>
+      <c r="K19" s="27"/>
+      <c r="L19" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="M19" s="26" t="s">
+      <c r="M19" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="N19" s="21" t="s">
+      <c r="N19" s="20" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="44"/>
-      <c r="B20" s="5" t="s">
+      <c r="A20" s="43"/>
+      <c r="B20" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F20" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="G20" s="6">
+      <c r="D20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="G20" s="5">
         <v>1</v>
       </c>
-      <c r="H20" s="6" t="s">
+      <c r="H20" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="I20" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="6" t="s">
+      <c r="I20" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="J20" s="5"/>
+      <c r="K20" s="5"/>
+      <c r="L20" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="M20" s="6" t="s">
+      <c r="M20" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="N20" s="17" t="s">
+      <c r="N20" s="16" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="44"/>
-      <c r="B21" s="5" t="s">
+      <c r="A21" s="43"/>
+      <c r="B21" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="5">
         <v>1</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="5">
         <v>4</v>
       </c>
-      <c r="F21" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="G21" s="6">
+      <c r="F21" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="G21" s="5">
         <v>1</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="H21" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="I21" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="J21" s="6"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6" t="s">
+      <c r="I21" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="J21" s="5"/>
+      <c r="K21" s="5"/>
+      <c r="L21" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="M21" s="6" t="s">
+      <c r="M21" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="N21" s="17" t="s">
+      <c r="N21" s="16" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="44"/>
-      <c r="B22" s="5" t="s">
+      <c r="A22" s="43"/>
+      <c r="B22" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E22" s="6">
+      <c r="D22" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" s="5">
         <v>250</v>
       </c>
-      <c r="F22" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="G22" s="6">
+      <c r="F22" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="G22" s="5">
         <v>1</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="H22" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="I22" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6" t="s">
+      <c r="I22" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5"/>
+      <c r="L22" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="M22" s="6" t="s">
+      <c r="M22" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="N22" s="17" t="s">
+      <c r="N22" s="16" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="44"/>
-      <c r="B23" s="5" t="s">
+      <c r="A23" s="43"/>
+      <c r="B23" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="G23" s="6">
+      <c r="D23" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F23" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="G23" s="5">
         <v>1</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="H23" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="I23" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6"/>
-      <c r="L23" s="6" t="s">
+      <c r="I23" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="M23" s="6" t="s">
+      <c r="M23" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="N23" s="17" t="s">
+      <c r="N23" s="16" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="37"/>
-      <c r="B24" s="18" t="s">
+      <c r="A24" s="36"/>
+      <c r="B24" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="18">
         <v>1</v>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="18">
         <v>4</v>
       </c>
-      <c r="F24" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="G24" s="19">
+      <c r="F24" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="G24" s="18">
         <v>1</v>
       </c>
-      <c r="H24" s="19" t="s">
+      <c r="H24" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="I24" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19" t="s">
+      <c r="I24" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="J24" s="18"/>
+      <c r="K24" s="18"/>
+      <c r="L24" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="M24" s="19" t="s">
+      <c r="M24" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="N24" s="20" t="s">
+      <c r="N24" s="19" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="26" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="48" t="s">
+      <c r="A26" s="46" t="s">
         <v>102</v>
       </c>
-      <c r="B26" s="31" t="s">
+      <c r="B26" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="32" t="s">
+      <c r="C26" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="D26" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="E26" s="32">
+      <c r="D26" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="E26" s="31">
         <v>30</v>
       </c>
-      <c r="F26" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="G26" s="32">
+      <c r="F26" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="G26" s="31">
         <v>1</v>
       </c>
-      <c r="H26" s="32" t="s">
+      <c r="H26" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="I26" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="J26" s="15" t="s">
+      <c r="I26" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="J26" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="K26" s="15" t="s">
+      <c r="K26" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="L26" s="15" t="s">
+      <c r="L26" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="M26" s="15" t="s">
+      <c r="M26" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="N26" s="16" t="s">
+      <c r="N26" s="15" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="41"/>
-      <c r="B27" s="53" t="s">
+      <c r="A27" s="40"/>
+      <c r="B27" s="51" t="s">
         <v>107</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E27" s="4">
+      <c r="D27" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E27" s="3">
         <v>50</v>
       </c>
-      <c r="F27" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="G27" s="6">
+      <c r="F27" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="G27" s="5">
         <v>1</v>
       </c>
-      <c r="H27" s="6" t="s">
+      <c r="H27" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="I27" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="4"/>
-      <c r="M27" s="4"/>
-      <c r="N27" s="52"/>
+      <c r="I27" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="50"/>
     </row>
     <row r="28" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="34"/>
-      <c r="B28" s="34" t="s">
-        <v>110</v>
-      </c>
-      <c r="C28" s="35" t="s">
+      <c r="A28" s="33"/>
+      <c r="B28" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="C28" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="D28" s="35" t="s">
-        <v>38</v>
-      </c>
-      <c r="E28" s="35" t="s">
-        <v>38</v>
-      </c>
-      <c r="F28" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="G28" s="35">
+      <c r="D28" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="F28" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="G28" s="34">
         <v>1</v>
       </c>
-      <c r="H28" s="35" t="s">
-        <v>109</v>
-      </c>
-      <c r="I28" s="35" t="s">
-        <v>38</v>
-      </c>
-      <c r="J28" s="35"/>
-      <c r="K28" s="35"/>
-      <c r="L28" s="35"/>
-      <c r="M28" s="35"/>
-      <c r="N28" s="36"/>
+      <c r="H28" s="34" t="s">
+        <v>108</v>
+      </c>
+      <c r="I28" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="35"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2098,115 +2156,115 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="23" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="24" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
+      <c r="A2" s="29"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
     </row>
     <row r="3" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="E3" s="33" t="s">
+      <c r="E3" s="32" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="37"/>
-      <c r="B4" s="35" t="s">
+      <c r="A4" s="36"/>
+      <c r="B4" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="D4" s="35" t="s">
+      <c r="D4" s="34" t="s">
         <v>99</v>
       </c>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="35" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
     </row>
     <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="C6" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="38" t="s">
+      <c r="D6" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="21" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="49" t="s">
+      <c r="A8" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="33" t="s">
+      <c r="E8" s="32" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="37"/>
-      <c r="B9" s="35" t="s">
+      <c r="A9" s="36"/>
+      <c r="B9" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="D9" s="35" t="s">
+      <c r="D9" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="36" t="s">
+      <c r="E9" s="35" t="s">
         <v>95</v>
       </c>
     </row>
